--- a/Data/EXCEL/Transfer/salemon/20240711/6756-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6756-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC240835-04F8-459D-BA97-032F9A593ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D3AC5C4-1D85-483B-A807-08F5F0DFC69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{17E7930E-50C3-4A80-A301-182FAE9ADF5F}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{E0DC4786-3317-4EC2-ABCF-FE0625FC2B90}"/>
   </bookViews>
   <sheets>
     <sheet name="6756-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,24 +1261,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B616AC5-5D71-4BF9-A713-CD5BED8F5745}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A41DF67-F546-437E-B213-F9E09EE73824}">
   <dimension ref="A1:Q124"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1387,7 +1387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1426,7 +1426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>-8.19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>-7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>-2.54</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>-31.1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>-33.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>-36.799999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>-38.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>-41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>-44</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>-48.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>-52.6</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>-57.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>-62</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>-64.400000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>-67.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>-8.16</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>-2.2200000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>35.299999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>70.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>66.099999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>34.9</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4500,312 +4500,312 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>43709</v>
       </c>
